--- a/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260630.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260630.xlsx
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>887,744,000</t>
+          <t>889,744,000</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>10.32%</t>
+          <t>10.28%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>10.24%</t>
+          <t>10.11%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>6.29%</t>
+          <t>5.99%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>5.00%</t>
+          <t>4.93%</t>
         </is>
       </c>
     </row>
@@ -699,34 +699,34 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>38,465,000</t>
+          <t>38,537,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>4.47%</t>
+          <t>4.39%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>112,174,000</t>
+          <t>4,979,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.41%</t>
+          <t>3.44%</t>
         </is>
       </c>
     </row>
@@ -748,51 +748,51 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.33%</t>
+          <t>3.38%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>93,988,442</t>
+          <t>112,174,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.24%</t>
+          <t>3.37%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>4,979,000</t>
+          <t>94,788,442</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.22%</t>
+          <t>3.33%</t>
         </is>
       </c>
     </row>
@@ -814,95 +814,95 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.11%</t>
+          <t>3.08%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>133,920,945</t>
+          <t>28,430,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.85%</t>
+          <t>2.91%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>28,430,000</t>
+          <t>25,824,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.69%</t>
+          <t>2.86%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>202607TX</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>台股期貨</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>25,824,000</t>
+          <t>1,872</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.68%</t>
+          <t>2.85%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>202607TX</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>台股期貨</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>1,772</t>
+          <t>134,019,945</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.67%</t>
+          <t>2.82%</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>30,516,000</t>
+          <t>30,666,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.64%</t>
+          <t>2.67%</t>
         </is>
       </c>
     </row>
@@ -946,51 +946,51 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.62%</t>
+          <t>2.58%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>遠傳</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>130,197,000</t>
+          <t>145,692,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.54%</t>
+          <t>2.49%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>台灣大</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>144,992,000</t>
+          <t>130,597,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.54%</t>
+          <t>2.48%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2.46%</t>
+          <t>2.42%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2.40%</t>
+          <t>2.32%</t>
         </is>
       </c>
     </row>
@@ -1051,12 +1051,12 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>98,167,000</t>
+          <t>98,567,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2.30%</t>
+          <t>2.27%</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2.18%</t>
+          <t>2.25%</t>
         </is>
       </c>
     </row>
@@ -1117,12 +1117,12 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>79,888,000</t>
+          <t>80,288,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>2.04%</t>
+          <t>2.07%</t>
         </is>
       </c>
     </row>
@@ -1139,100 +1139,100 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>270,866,000</t>
+          <t>272,366,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.97%</t>
+          <t>1.99%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>51,717,000</t>
+          <t>178,956,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.92%</t>
+          <t>1.94%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>統一超</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>178,956,000</t>
+          <t>51,717,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.90%</t>
+          <t>1.88%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>鈊  象</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>14,293,000</t>
+          <t>33,450,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.82%</t>
+          <t>1.87%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>鈊  象</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>33,450,000</t>
+          <t>14,343,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.80%</t>
+          <t>1.84%</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.72%</t>
+          <t>1.69%</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>1.62%</t>
+          <t>1.63%</t>
         </is>
       </c>
     </row>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>4,274,033,547</t>
+          <t>4,635,619,240</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr"/>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>10,621,907,703</t>
+          <t>11,054,588,296</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr"/>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>-135,186,363</t>
+          <t>-383,754,106</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr"/>
